--- a/src/test/resources/network/brightspots/rcv/test_data/_shared/simple_sequential_cvr.xlsx
+++ b/src/test/resources/network/brightspots/rcv/test_data/_shared/simple_sequential_cvr.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="9">
   <si>
     <t>Ballot #</t>
   </si>
@@ -26,6 +26,9 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>undervote</t>
   </si>
   <si>
     <t>B</t>
@@ -1230,8 +1233,12 @@
       <c r="B2" t="s" s="2">
         <v>4</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="C2" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3" ht="13.55" customHeight="1">
@@ -1241,8 +1248,12 @@
       <c r="B3" t="s" s="2">
         <v>4</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+      <c r="C3" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" ht="13.55" customHeight="1">
@@ -1252,8 +1263,12 @@
       <c r="B4" t="s" s="2">
         <v>4</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="C4" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" ht="13.55" customHeight="1">
@@ -1263,8 +1278,12 @@
       <c r="B5" t="s" s="2">
         <v>4</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+      <c r="C5" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" ht="13.55" customHeight="1">
@@ -1275,9 +1294,11 @@
         <v>4</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>5</v>
-      </c>
-      <c r="D6" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7" ht="13.55" customHeight="1">
@@ -1285,10 +1306,14 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8" ht="13.55" customHeight="1">
@@ -1296,10 +1321,14 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E8" s="3"/>
     </row>
     <row r="9" ht="13.55" customHeight="1">
@@ -1307,10 +1336,14 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E9" s="3"/>
     </row>
     <row r="10" ht="13.55" customHeight="1">
@@ -1318,10 +1351,14 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="E10" s="3"/>
     </row>
   </sheetData>
